--- a/results/catalyst_calculations.xlsx
+++ b/results/catalyst_calculations.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{324500AA-9169-4EB8-9A96-B3F18A3CC321}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C47FA6-D7EC-4291-8D23-C993FD6F344C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13125" xr2:uid="{BA5C6C5E-8C6D-4143-A1D5-EF086195B278}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="9210" activeTab="1" xr2:uid="{BA5C6C5E-8C6D-4143-A1D5-EF086195B278}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="catalyst_N2O" sheetId="1" r:id="rId1"/>
+    <sheet name="catalyst_H2O2" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>Here you have the data: - 2Au-PrOx</t>
   </si>
@@ -33,18 +34,12 @@
     <t>Selectivity / -: N2O 0.887 N2 0.104 NO 0.009 at full conversion</t>
   </si>
   <si>
-    <t>Productivity / kgN2O kgcat-1 h-1:  2.08956 (can be further increased - note that in this result is per hour, while in the table there is no reference to time) </t>
-  </si>
-  <si>
     <t>Metal content / wt%: 1.91</t>
   </si>
   <si>
     <t>Metal recovery / %: 99</t>
   </si>
   <si>
-    <t>Productivity / kgN2O per kgCat per hr</t>
-  </si>
-  <si>
     <t>Metal content / wt%</t>
   </si>
   <si>
@@ -61,6 +56,105 @@
   </si>
   <si>
     <t>100% recovery of PrOx</t>
+  </si>
+  <si>
+    <t>kd: 0.001</t>
+  </si>
+  <si>
+    <t>Cost of gold 2022</t>
+  </si>
+  <si>
+    <t>troy oz per kg</t>
+  </si>
+  <si>
+    <t>$ per kg N2O</t>
+  </si>
+  <si>
+    <t>Impact of gold</t>
+  </si>
+  <si>
+    <t>kg CO2e per kg gold</t>
+  </si>
+  <si>
+    <t>$ per troy oz gold</t>
+  </si>
+  <si>
+    <t>$ per kg gold</t>
+  </si>
+  <si>
+    <t>kg CO2e per kg N2O</t>
+  </si>
+  <si>
+    <t>STY / kgN2O kgcat-1 h-1:  2.08956 (can be further increased - note that in this result is per hour, while in the table there is no reference to time) </t>
+  </si>
+  <si>
+    <t>Here you have the data: - Pd black</t>
+  </si>
+  <si>
+    <t>kd: 0.00114</t>
+  </si>
+  <si>
+    <t>Productivity / kg H2O2 per kgCat</t>
+  </si>
+  <si>
+    <t>STY / kg H2O2 per kgCat per hr</t>
+  </si>
+  <si>
+    <t>STY / kg N2O per kgCat per hr</t>
+  </si>
+  <si>
+    <t>Productivity / kg N2O per kgCat</t>
+  </si>
+  <si>
+    <t>Total H2O2 production / kg H2O2 per kgCat per hr</t>
+  </si>
+  <si>
+    <t>Metal content / wt%: 0.3</t>
+  </si>
+  <si>
+    <t>STY/ kgH2O2 kgcat-1 h-1:  66.67</t>
+  </si>
+  <si>
+    <t>kg metal per kg H2O2</t>
+  </si>
+  <si>
+    <t>kg metal fed per kg H2O2</t>
+  </si>
+  <si>
+    <t>Cost of Pd 2022</t>
+  </si>
+  <si>
+    <t>$ per troy oz Pd</t>
+  </si>
+  <si>
+    <t>$ per kg H2O2</t>
+  </si>
+  <si>
+    <t>Impact of palladium</t>
+  </si>
+  <si>
+    <t>kg CO2e per kg palladium</t>
+  </si>
+  <si>
+    <t>$ per kg Pd</t>
+  </si>
+  <si>
+    <t>kg CO2e per kg H2O2</t>
+  </si>
+  <si>
+    <t>Metal recovery / %: 95</t>
+  </si>
+  <si>
+    <t>https://doi.org/10.1016/j.cep.2006.12.012</t>
+  </si>
+  <si>
+    <t>https://pubs.acs.org/doi/10.1021/ie00026a016</t>
+  </si>
+  <si>
+    <t>https://www.macrotrends.net/2542/palladium-prices-historical-chart-data</t>
+  </si>
+  <si>
+    <t>World bank</t>
   </si>
 </sst>
 </file>
@@ -68,7 +162,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="170" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -93,18 +187,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -134,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -143,14 +231,30 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -466,88 +570,338 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4252B3-80EE-4C59-BFC3-E460B32D2F1E}">
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.28515625" customWidth="1"/>
-    <col min="2" max="2" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="34.26953125" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="5">
+        <v>2.0895600000000001</v>
+      </c>
+      <c r="B10" s="6">
+        <f>A10/0.001</f>
+        <v>2089.56</v>
+      </c>
+      <c r="C10" s="7">
+        <f>B10</f>
+        <v>2089.56</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1.91</v>
+      </c>
+      <c r="E10" s="2">
+        <v>99</v>
+      </c>
+      <c r="F10" s="8">
+        <f>D10/100/C10</f>
+        <v>9.1406803346158993E-6</v>
+      </c>
+      <c r="G10" s="8">
+        <f>F10*(1-E10/100)</f>
+        <v>9.1406803346159078E-8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <v>1800.6025</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="10">
+        <v>32.150700000000001</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="10">
+        <f>A13*A14</f>
+        <v>57890.630796750003</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="12">
+        <f>A15*G10</f>
+        <v>5.2915975048236277E-3</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="10">
+        <v>50268.611278060896</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="12">
+        <f>A19*G10</f>
+        <v>4.5948930655782269E-3</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEBE742-6987-4C1C-A128-3A6EC1D88F41}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="34.26953125" customWidth="1"/>
+    <col min="2" max="2" width="40.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+        <v>38</v>
+      </c>
+      <c r="B4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="5">
-        <v>2.0895600000000001</v>
-      </c>
-      <c r="B9" s="6">
-        <v>2.0895600000000001</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1.91</v>
-      </c>
-      <c r="D9" s="2">
-        <v>99</v>
-      </c>
-      <c r="E9" s="6">
-        <f>C9/100/B9</f>
-        <v>9.1406803346158992E-3</v>
-      </c>
-      <c r="F9" s="6">
-        <f>E9*(100-D9)/100</f>
-        <v>9.1406803346158989E-5</v>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
+        <f>1600/24</f>
+        <v>66.666666666666671</v>
+      </c>
+      <c r="B8" s="6">
+        <f>A8/0.00114</f>
+        <v>58479.532163742697</v>
+      </c>
+      <c r="C8" s="7">
+        <f>B8</f>
+        <v>58479.532163742697</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>95</v>
+      </c>
+      <c r="F8" s="8">
+        <f>D8/100/C8</f>
+        <v>5.1299999999999996E-8</v>
+      </c>
+      <c r="G8" s="8">
+        <f>F8*(1-E8/100)</f>
+        <v>2.5650000000000022E-9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="10">
+        <v>2064.451599</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="10">
+        <v>32.150700000000001</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="10">
+        <f>A11*A12</f>
+        <v>66373.564023969302</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="12">
+        <f>A13*G8</f>
+        <v>1.702481917214814E-4</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="10">
+        <v>11612.105017427701</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="12">
+        <f>A17*G8</f>
+        <v>2.9785049369702079E-5</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/results/catalyst_calculations.xlsx
+++ b/results/catalyst_calculations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Side projects\Nitrous oxide production\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8C47FA6-D7EC-4291-8D23-C993FD6F344C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{731ECA7F-1DA7-4C0F-8613-B9F0009F36BD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16200" windowHeight="9210" activeTab="1" xr2:uid="{BA5C6C5E-8C6D-4143-A1D5-EF086195B278}"/>
   </bookViews>
@@ -571,53 +571,53 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA4252B3-80EE-4C59-BFC3-E460B32D2F1E}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="34.26953125" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="34.28515625" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
@@ -640,7 +640,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2.0895600000000001</v>
       </c>
@@ -667,12 +667,12 @@
         <v>9.1406803346159078E-8</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>1800.6025</v>
       </c>
@@ -683,7 +683,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>32.150700000000001</v>
       </c>
@@ -691,7 +691,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <f>A13*A14</f>
         <v>57890.630796750003</v>
@@ -700,7 +700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <f>A15*G10</f>
         <v>5.2915975048236277E-3</v>
@@ -709,12 +709,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>50268.611278060896</v>
       </c>
@@ -722,7 +722,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <f>A19*G10</f>
         <v>4.5948930655782269E-3</v>
@@ -740,24 +740,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDEBE742-6987-4C1C-A128-3A6EC1D88F41}">
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.26953125" customWidth="1"/>
-    <col min="2" max="2" width="40.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="2" max="2" width="40.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.54296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:7" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>28</v>
       </c>
@@ -765,7 +765,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>27</v>
       </c>
@@ -773,7 +773,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>38</v>
       </c>
@@ -781,7 +781,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -789,7 +789,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
@@ -812,7 +812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>1600/24</f>
         <v>66.666666666666671</v>
@@ -840,12 +840,12 @@
         <v>2.5650000000000022E-9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>2064.451599</v>
       </c>
@@ -856,7 +856,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>32.150700000000001</v>
       </c>
@@ -864,7 +864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <f>A11*A12</f>
         <v>66373.564023969302</v>
@@ -873,7 +873,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <f>A13*G8</f>
         <v>1.702481917214814E-4</v>
@@ -882,12 +882,12 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>11612.105017427701</v>
       </c>
@@ -895,7 +895,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <f>A17*G8</f>
         <v>2.9785049369702079E-5</v>
